--- a/end2end/top1_target_drug_per_query_tables.xlsx
+++ b/end2end/top1_target_drug_per_query_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\troy\Documents\GitHub\coder_data\end2end\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53517E58-A38E-4E0B-AD51-A504385D1928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDC963D-D97C-44E3-9152-B5C465A167AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="185">
   <si>
     <t>Dataset</t>
   </si>
@@ -564,6 +564,26 @@
   </si>
   <si>
     <t>d049</t>
+  </si>
+  <si>
+    <t>去掉</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>drug_q003</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>drug_q006</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>drug_q015</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1666,7 +1686,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1675,7 +1695,7 @@
     <col min="5" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="42">
+    <row r="1" spans="1:18" ht="42">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1728,7 +1748,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
         <v>53</v>
       </c>
@@ -1781,7 +1801,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
         <v>59</v>
       </c>
@@ -1834,9 +1854,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>54</v>
@@ -1886,8 +1906,11 @@
       <c r="Q4" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
         <v>66</v>
       </c>
@@ -1940,7 +1963,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -1993,9 +2016,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>54</v>
@@ -2045,8 +2068,11 @@
       <c r="Q7" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
         <v>76</v>
       </c>
@@ -2099,7 +2125,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
         <v>79</v>
       </c>
@@ -2152,7 +2178,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
         <v>82</v>
       </c>
@@ -2205,7 +2231,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
         <v>85</v>
       </c>
@@ -2258,7 +2284,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
         <v>88</v>
       </c>
@@ -2311,7 +2337,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
         <v>91</v>
       </c>
@@ -2364,7 +2390,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
         <v>94</v>
       </c>
@@ -2417,7 +2443,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
         <v>97</v>
       </c>
@@ -2470,9 +2496,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>67</v>
@@ -2521,6 +2547,9 @@
       </c>
       <c r="Q16" s="5" t="s">
         <v>58</v>
+      </c>
+      <c r="R16" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -3932,7 +3961,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3941,7 +3970,7 @@
     <col min="5" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="42">
+    <row r="1" spans="1:18" ht="42">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -3994,7 +4023,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
         <v>120</v>
       </c>
@@ -4047,7 +4076,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
         <v>123</v>
       </c>
@@ -4099,8 +4128,11 @@
       <c r="Q3" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
         <v>126</v>
       </c>
@@ -4153,7 +4185,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
         <v>129</v>
       </c>
@@ -4206,7 +4238,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
         <v>132</v>
       </c>
@@ -4259,7 +4291,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
         <v>135</v>
       </c>
@@ -4312,7 +4344,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
         <v>138</v>
       </c>
@@ -4365,7 +4397,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
         <v>141</v>
       </c>
@@ -4418,7 +4450,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
         <v>144</v>
       </c>
@@ -4471,7 +4503,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
         <v>147</v>
       </c>
@@ -4523,8 +4555,11 @@
       <c r="Q11" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="R11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
         <v>150</v>
       </c>
@@ -4576,8 +4611,11 @@
       <c r="Q12" s="5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="R12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
         <v>153</v>
       </c>
@@ -4630,7 +4668,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
         <v>156</v>
       </c>
@@ -4683,7 +4721,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
         <v>159</v>
       </c>
@@ -4736,7 +4774,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
         <v>162</v>
       </c>
